--- a/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/1778676142095 dated 4.6.26 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/1778676142095 dated 4.6.26 - parsed.xlsx
@@ -427,7 +427,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.643Z</v>
+        <v>2026-07-14T13:50:04.431Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/1778676142095 dated 4.6.26 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/12-lordship-9035-q1-2026/parsed-excel/1778676142095 dated 4.6.26 - parsed.xlsx
@@ -427,7 +427,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:04.431Z</v>
+        <v>2026-07-17T19:29:58.197Z</v>
       </c>
     </row>
     <row r="5">
